--- a/backend/data-filtering/stops_table.xlsx
+++ b/backend/data-filtering/stops_table.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\travel\backend\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\travel\backend\data-filtering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D5B24ED-1DE4-4245-8770-78C6D8F4A39D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC8416C-F8E5-468C-981B-7FED838B7EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{0946D8EF-606D-4B7F-92DD-E4F456A214B3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{0946D8EF-606D-4B7F-92DD-E4F456A214B3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/backend/data-filtering/stops_table.xlsx
+++ b/backend/data-filtering/stops_table.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\travel\backend\data-filtering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC8416C-F8E5-468C-981B-7FED838B7EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88399696-8129-4975-AB66-594A2A664596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{0946D8EF-606D-4B7F-92DD-E4F456A214B3}"/>
   </bookViews>
@@ -36,204 +36,225 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="73">
   <si>
     <t>stop_id</t>
   </si>
   <si>
-    <t>lat</t>
-  </si>
-  <si>
-    <t>lng</t>
-  </si>
-  <si>
     <t>mode</t>
   </si>
   <si>
-    <t>landmark_hint</t>
-  </si>
-  <si>
-    <t>CHURCHGATE</t>
-  </si>
-  <si>
-    <t>Marine Lines</t>
-  </si>
-  <si>
-    <t>Charni Road</t>
-  </si>
-  <si>
-    <t>Grant Road</t>
-  </si>
-  <si>
-    <t>M'BAI CENTRAL (L)</t>
-  </si>
-  <si>
-    <t>Mahalakshmi</t>
-  </si>
-  <si>
-    <t>Lower Parel</t>
-  </si>
-  <si>
-    <t>Prabhadevi</t>
-  </si>
-  <si>
-    <t>DADAR</t>
-  </si>
-  <si>
-    <t>Matunga Road</t>
-  </si>
-  <si>
-    <t>Mahim Jn.</t>
-  </si>
-  <si>
-    <t>BANDRA</t>
-  </si>
-  <si>
     <t>Khar Road</t>
   </si>
   <si>
-    <t>Santa Cruz</t>
-  </si>
-  <si>
-    <t>Vile Parle</t>
-  </si>
-  <si>
-    <t>ANDHERI</t>
-  </si>
-  <si>
     <t>Jogeshwari</t>
   </si>
   <si>
-    <t>Ram Mandir</t>
-  </si>
-  <si>
     <t>Goregaon</t>
   </si>
   <si>
-    <t>Malad</t>
-  </si>
-  <si>
-    <t>Kandivli</t>
-  </si>
-  <si>
-    <t>BORIVALI</t>
-  </si>
-  <si>
-    <t>Dahisar</t>
-  </si>
-  <si>
-    <t>Mira Road</t>
-  </si>
-  <si>
-    <t>Bhayandar</t>
-  </si>
-  <si>
-    <t>Naigaon</t>
-  </si>
-  <si>
-    <t>Vasai Road</t>
-  </si>
-  <si>
-    <t>Nalla Sopara</t>
-  </si>
-  <si>
-    <t>VIRAR</t>
-  </si>
-  <si>
-    <t>CHU_WR</t>
-  </si>
-  <si>
-    <t>DAD_WR</t>
-  </si>
-  <si>
-    <t>BAN_WR</t>
-  </si>
-  <si>
-    <t>AND_WR</t>
-  </si>
-  <si>
-    <t>BOR_WR</t>
-  </si>
-  <si>
-    <t>VIR_WR</t>
-  </si>
-  <si>
-    <t>MAR_WR</t>
-  </si>
-  <si>
-    <t>CHA_WR</t>
-  </si>
-  <si>
-    <t>GRA_WR</t>
-  </si>
-  <si>
-    <t>MAH_WR</t>
-  </si>
-  <si>
-    <t>LOW_WR</t>
-  </si>
-  <si>
-    <t>PRA_WR</t>
-  </si>
-  <si>
-    <t>MAT_WR</t>
-  </si>
-  <si>
-    <t>KHA_WR</t>
-  </si>
-  <si>
-    <t>SAN_WR</t>
-  </si>
-  <si>
-    <t>VIL_WR</t>
-  </si>
-  <si>
-    <t>JOG_WR</t>
-  </si>
-  <si>
-    <t>RAM_WR</t>
-  </si>
-  <si>
-    <t>GOR_WR</t>
-  </si>
-  <si>
-    <t>MAL_WR</t>
-  </si>
-  <si>
-    <t>KAN_WR</t>
-  </si>
-  <si>
-    <t>DAH_WR</t>
-  </si>
-  <si>
-    <t>MIR_WR</t>
-  </si>
-  <si>
-    <t>BHA_WR</t>
-  </si>
-  <si>
-    <t>NAI_WR</t>
-  </si>
-  <si>
-    <t>VAS_WR</t>
-  </si>
-  <si>
-    <t>NAL_WR</t>
-  </si>
-  <si>
-    <t>MUB_WR</t>
-  </si>
-  <si>
     <t>LOCALTR</t>
   </si>
   <si>
     <t>name</t>
   </si>
   <si>
-    <t>is_interchange</t>
-  </si>
-  <si>
-    <t>MAK_WR</t>
+    <t>Panvel</t>
+  </si>
+  <si>
+    <t>Khandeshwar</t>
+  </si>
+  <si>
+    <t>Mansarovar</t>
+  </si>
+  <si>
+    <t>Kharghar</t>
+  </si>
+  <si>
+    <t>Belapur CBD</t>
+  </si>
+  <si>
+    <t>Seawood Darave</t>
+  </si>
+  <si>
+    <t>Nerul</t>
+  </si>
+  <si>
+    <t>Juinagar</t>
+  </si>
+  <si>
+    <t>Sanpada</t>
+  </si>
+  <si>
+    <t>Vashi</t>
+  </si>
+  <si>
+    <t>Mankhurd</t>
+  </si>
+  <si>
+    <t>Govandi</t>
+  </si>
+  <si>
+    <t>Chembur</t>
+  </si>
+  <si>
+    <t>Tilaknagar</t>
+  </si>
+  <si>
+    <t>Kurla</t>
+  </si>
+  <si>
+    <t>Chunabhatti</t>
+  </si>
+  <si>
+    <t>GTB Nagar</t>
+  </si>
+  <si>
+    <t>Ramnagar</t>
+  </si>
+  <si>
+    <t>Andheri</t>
+  </si>
+  <si>
+    <t>Vileparle</t>
+  </si>
+  <si>
+    <t>Santacruz</t>
+  </si>
+  <si>
+    <t>Bandra</t>
+  </si>
+  <si>
+    <t>Mahim Jn</t>
+  </si>
+  <si>
+    <t>King's Circle</t>
+  </si>
+  <si>
+    <t>Vadala Road</t>
+  </si>
+  <si>
+    <t>Sewri</t>
+  </si>
+  <si>
+    <t>Cotton Green</t>
+  </si>
+  <si>
+    <t>Reay Road</t>
+  </si>
+  <si>
+    <t>Dockyard Road</t>
+  </si>
+  <si>
+    <t>Sandhurst Road</t>
+  </si>
+  <si>
+    <t>Masjid</t>
+  </si>
+  <si>
+    <t>Mumbai CSMT</t>
+  </si>
+  <si>
+    <t>BEL_HR</t>
+  </si>
+  <si>
+    <t>KAG_HR</t>
+  </si>
+  <si>
+    <t>MAN_HR</t>
+  </si>
+  <si>
+    <t>SWD_HR</t>
+  </si>
+  <si>
+    <t>NER_HR</t>
+  </si>
+  <si>
+    <t>JUI_HR</t>
+  </si>
+  <si>
+    <t>SAN_HR</t>
+  </si>
+  <si>
+    <t>VAS_HR</t>
+  </si>
+  <si>
+    <t>GOV_HR</t>
+  </si>
+  <si>
+    <t>CHEM_HR</t>
+  </si>
+  <si>
+    <t>TIK_HR</t>
+  </si>
+  <si>
+    <t>KUR_HR</t>
+  </si>
+  <si>
+    <t>CBH_HR</t>
+  </si>
+  <si>
+    <t>GTB_HR</t>
+  </si>
+  <si>
+    <t>GOR_HR</t>
+  </si>
+  <si>
+    <t>RAM_HR</t>
+  </si>
+  <si>
+    <t>JOG_HR</t>
+  </si>
+  <si>
+    <t>AND_HR</t>
+  </si>
+  <si>
+    <t>VPR_HR</t>
+  </si>
+  <si>
+    <t>STZ_HR</t>
+  </si>
+  <si>
+    <t>KHR_HR</t>
+  </si>
+  <si>
+    <t>BAN_HR</t>
+  </si>
+  <si>
+    <t>MAH_HR</t>
+  </si>
+  <si>
+    <t>KCI_HR</t>
+  </si>
+  <si>
+    <t>VAD_HR</t>
+  </si>
+  <si>
+    <t>SEW_HR</t>
+  </si>
+  <si>
+    <t>CGR_HR</t>
+  </si>
+  <si>
+    <t>RRD_HR</t>
+  </si>
+  <si>
+    <t>DOC_HR</t>
+  </si>
+  <si>
+    <t>SRD_HR</t>
+  </si>
+  <si>
+    <t>MAS_HR</t>
+  </si>
+  <si>
+    <t>CST_HR</t>
+  </si>
+  <si>
+    <t>KAN_HR</t>
+  </si>
+  <si>
+    <t>PAN_HR</t>
   </si>
 </sst>
 </file>
@@ -279,7 +300,7 @@
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -615,349 +636,407 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BF0ABC8-519B-43D1-89B4-419028B1B4FB}">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.5546875" customWidth="1"/>
+    <col min="2" max="2" width="17.109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>41</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>65</v>
-      </c>
       <c r="B7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="B9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>35</v>
-      </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>46</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="C15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="C16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+      <c r="C18" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="C19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="C20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="C21" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E22" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C22" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E24" t="s">
+      <c r="C24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>56</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E25" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>57</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E26" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>58</v>
-      </c>
-      <c r="B27" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E27" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>59</v>
-      </c>
-      <c r="B28" s="1" t="s">
+      <c r="C28" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>63</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E28" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>60</v>
-      </c>
-      <c r="B29" s="1" t="s">
+      <c r="C29" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E29" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="1" t="s">
+      <c r="C30" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>65</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E30" t="s">
-        <v>62</v>
+      <c r="C31" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>66</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>67</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>68</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>69</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/backend/data-filtering/stops_table.xlsx
+++ b/backend/data-filtering/stops_table.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\travel\backend\data-filtering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88399696-8129-4975-AB66-594A2A664596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD605BA1-1CFD-426A-B87A-99052F35D84C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{0946D8EF-606D-4B7F-92DD-E4F456A214B3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="74">
   <si>
     <t>stop_id</t>
   </si>
@@ -255,6 +255,9 @@
   </si>
   <si>
     <t>PAN_HR</t>
+  </si>
+  <si>
+    <t>MNK_HR</t>
   </si>
 </sst>
 </file>
@@ -766,7 +769,7 @@
     </row>
     <row r="12" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>17</v>
